--- a/docs/shm_diagrama_despliegue.xlsx
+++ b/docs/shm_diagrama_despliegue.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PROYECTOS\SAN_PABLO\02_HHMM\Desarrollo\ADG_SHM\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C63CFDB-85CB-4C68-BFEA-D6842FA7C087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77DF94F6-EF62-4D4A-BB8A-2FFABF75F2FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{86EF7CFC-75BA-4FD8-A433-F01FE68532FB}"/>
   </bookViews>
@@ -282,11 +282,11 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -692,8 +692,8 @@
       </c>
     </row>
     <row r="43" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="13"/>
-      <c r="C43" s="13"/>
+      <c r="B43" s="14"/>
+      <c r="C43" s="14"/>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
       <c r="F43" s="4"/>
@@ -749,7 +749,7 @@
       <c r="H45" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I45" s="14" t="s">
+      <c r="I45" s="13" t="s">
         <v>34</v>
       </c>
       <c r="J45" s="6"/>
@@ -772,7 +772,7 @@
       <c r="H46" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I46" s="14" t="s">
+      <c r="I46" s="13" t="s">
         <v>35</v>
       </c>
       <c r="J46" s="6"/>
@@ -795,7 +795,7 @@
       <c r="H47" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I47" s="14" t="s">
+      <c r="I47" s="13" t="s">
         <v>36</v>
       </c>
       <c r="J47" s="6"/>
@@ -818,7 +818,7 @@
       <c r="H48" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I48" s="14" t="s">
+      <c r="I48" s="13" t="s">
         <v>37</v>
       </c>
       <c r="J48" s="6"/>
@@ -908,7 +908,7 @@
       <c r="H52" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I52" s="14" t="s">
+      <c r="I52" s="13" t="s">
         <v>38</v>
       </c>
       <c r="J52" s="6"/>

--- a/docs/shm_diagrama_despliegue.xlsx
+++ b/docs/shm_diagrama_despliegue.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PROYECTOS\SAN_PABLO\02_HHMM\Desarrollo\ADG_SHM\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77DF94F6-EF62-4D4A-BB8A-2FFABF75F2FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{790ECF32-5FBE-49F1-AC5C-0C4853573167}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{86EF7CFC-75BA-4FD8-A433-F01FE68532FB}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="40">
   <si>
     <t>Componentes</t>
   </si>
@@ -156,6 +156,9 @@
   </si>
   <si>
     <t>whm.notificaciones@sanpablo.com.pe</t>
+  </si>
+  <si>
+    <t>ssss</t>
   </si>
 </sst>
 </file>
@@ -254,7 +257,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -287,6 +290,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -913,6 +919,11 @@
       </c>
       <c r="J52" s="6"/>
     </row>
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C54" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
     <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="G55" s="11"/>
     </row>

--- a/docs/shm_diagrama_despliegue.xlsx
+++ b/docs/shm_diagrama_despliegue.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PROYECTOS\SAN_PABLO\02_HHMM\Desarrollo\ADG_SHM\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{790ECF32-5FBE-49F1-AC5C-0C4853573167}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{580BBFDD-5F1E-4ACA-B71D-C852556A9422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{86EF7CFC-75BA-4FD8-A433-F01FE68532FB}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="39">
   <si>
     <t>Componentes</t>
   </si>
@@ -156,9 +156,6 @@
   </si>
   <si>
     <t>whm.notificaciones@sanpablo.com.pe</t>
-  </si>
-  <si>
-    <t>ssss</t>
   </si>
 </sst>
 </file>
@@ -288,11 +285,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -698,8 +695,8 @@
       </c>
     </row>
     <row r="43" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
+      <c r="B43" s="15"/>
+      <c r="C43" s="15"/>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
       <c r="F43" s="4"/>
@@ -750,7 +747,7 @@
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
       <c r="G45" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H45" s="1" t="s">
         <v>12</v>
@@ -773,7 +770,7 @@
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
       <c r="G46" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H46" s="1" t="s">
         <v>12</v>
@@ -920,9 +917,7 @@
       <c r="J52" s="6"/>
     </row>
     <row r="54" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C54" s="15" t="s">
-        <v>39</v>
-      </c>
+      <c r="C54" s="14"/>
     </row>
     <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="G55" s="11"/>

--- a/docs/shm_diagrama_despliegue.xlsx
+++ b/docs/shm_diagrama_despliegue.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PROYECTOS\SAN_PABLO\02_HHMM\Desarrollo\ADG_SHM\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{580BBFDD-5F1E-4ACA-B71D-C852556A9422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3985FFD9-C28A-42EA-893D-978F9EA174BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{86EF7CFC-75BA-4FD8-A433-F01FE68532FB}"/>
   </bookViews>
@@ -162,7 +162,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -211,6 +211,15 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -254,7 +263,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -290,6 +299,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -775,7 +787,7 @@
       <c r="H46" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I46" s="13" t="s">
+      <c r="I46" s="16" t="s">
         <v>35</v>
       </c>
       <c r="J46" s="6"/>

--- a/docs/shm_diagrama_despliegue.xlsx
+++ b/docs/shm_diagrama_despliegue.xlsx
@@ -1,35 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PROYECTOS\SAN_PABLO\02_HHMM\Desarrollo\ADG_SHM\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Fuentes SGD\ADG_HHMM v1\ADG_SHM\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3985FFD9-C28A-42EA-893D-978F9EA174BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C844A09-F634-4AD5-9D42-1DBDAD78C5BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{86EF7CFC-75BA-4FD8-A433-F01FE68532FB}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Diagrama Despliegue" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -39,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="41">
   <si>
     <t>Componentes</t>
   </si>
@@ -155,14 +144,20 @@
     <t>https://apiint.sanpablo.com.pe</t>
   </si>
   <si>
-    <t>whm.notificaciones@sanpablo.com.pe</t>
+    <t>mail.sanpablo.com.pe</t>
+  </si>
+  <si>
+    <t>Correo : whm.notificaciones@sanpablo.com.pe</t>
+  </si>
+  <si>
+    <t>En test  : https://190.12.87.190:8124</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -211,15 +206,6 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
-    <font>
-      <b/>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -263,7 +249,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -278,7 +264,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -291,17 +276,15 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -326,22 +309,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>85725</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>61331</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>94881</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>295275</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>187492</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2371328</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>77702</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Imagen 1">
+        <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{71E2D861-3274-A054-B2DF-4FC5D8D79F2F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F7429AC-B2B6-46C6-9240-3F3D964A2F9C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -349,16 +332,15 @@
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
-      <xdr:blipFill>
+      <xdr:blipFill rotWithShape="1">
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
+        <a:srcRect b="26357"/>
+        <a:stretch/>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="847725" y="190500"/>
-          <a:ext cx="12230100" cy="7616992"/>
+          <a:off x="894769" y="94881"/>
+          <a:ext cx="12509684" cy="7840946"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -687,212 +669,97 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B9FB65D-DA82-419A-9D83-304785E367CD}">
-  <dimension ref="B42:J56"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B47:J61"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="4" customWidth="1"/>
-    <col min="3" max="3" width="29.42578125" customWidth="1"/>
-    <col min="4" max="4" width="34.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.85546875" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" customWidth="1"/>
-    <col min="7" max="7" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.140625" customWidth="1"/>
-    <col min="9" max="9" width="46.42578125" customWidth="1"/>
-    <col min="10" max="10" width="41.140625" customWidth="1"/>
+    <col min="3" max="3" width="29.375" customWidth="1"/>
+    <col min="4" max="4" width="34.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.875" customWidth="1"/>
+    <col min="6" max="6" width="10.75" customWidth="1"/>
+    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.125" customWidth="1"/>
+    <col min="9" max="9" width="46.375" customWidth="1"/>
+    <col min="10" max="10" width="41.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B42" s="7" t="s">
+    <row r="47" spans="2:10" ht="15">
+      <c r="B47" s="6" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="15"/>
-      <c r="C43" s="15"/>
-      <c r="D43" s="4"/>
-      <c r="E43" s="4"/>
-      <c r="F43" s="4"/>
-      <c r="G43" s="4"/>
-      <c r="H43" s="4"/>
-      <c r="I43" s="4"/>
-      <c r="J43" s="5"/>
-    </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B44" s="8" t="s">
+    <row r="48" spans="2:10" ht="15" customHeight="1">
+      <c r="B48" s="15"/>
+      <c r="C48" s="15"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="5"/>
+    </row>
+    <row r="49" spans="2:10">
+      <c r="B49" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C44" s="9" t="s">
+      <c r="C49" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D44" s="9" t="s">
+      <c r="D49" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E44" s="9" t="s">
+      <c r="E49" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F44" s="10" t="s">
+      <c r="F49" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="G44" s="9" t="s">
+      <c r="G49" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H44" s="9" t="s">
+      <c r="H49" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I44" s="9" t="s">
+      <c r="I49" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="J44" s="9" t="s">
+      <c r="J49" s="8" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B45" s="1">
+    <row r="50" spans="2:10">
+      <c r="B50" s="1">
         <v>1</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C50" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="D50" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="E45" s="3"/>
-      <c r="F45" s="3"/>
-      <c r="G45" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H45" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I45" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="J45" s="6"/>
-    </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B46" s="1">
-        <v>2</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E46" s="3"/>
-      <c r="F46" s="3"/>
-      <c r="G46" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I46" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="J46" s="6"/>
-    </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B47" s="1">
-        <v>3</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E47" s="3"/>
-      <c r="F47" s="3"/>
-      <c r="G47" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H47" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I47" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="J47" s="6"/>
-    </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B48" s="1">
-        <v>4</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E48" s="3"/>
-      <c r="F48" s="3"/>
-      <c r="G48" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H48" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I48" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="J48" s="6"/>
-    </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B49" s="1">
-        <v>5</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F49" s="3"/>
-      <c r="G49" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H49" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I49" s="3"/>
-      <c r="J49" s="12" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B50" s="1">
-        <v>6</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
       <c r="G50" s="1" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I50" s="3"/>
-      <c r="J50" s="6"/>
-    </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I50" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="J50" s="14"/>
+    </row>
+    <row r="51" spans="2:10">
       <c r="B51" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
@@ -900,53 +767,172 @@
         <v>11</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I51" s="3"/>
-      <c r="J51" s="6"/>
-    </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="I51" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="J51" s="14"/>
+    </row>
+    <row r="52" spans="2:10">
       <c r="B52" s="1">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
       <c r="G52" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I52" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="J52" s="14"/>
+    </row>
+    <row r="53" spans="2:10">
+      <c r="B53" s="1">
+        <v>4</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I53" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="J53" s="14"/>
+    </row>
+    <row r="54" spans="2:10">
+      <c r="B54" s="1">
+        <v>5</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F54" s="3"/>
+      <c r="G54" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I54" s="3"/>
+      <c r="J54" s="11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="55" spans="2:10">
+      <c r="B55" s="1">
+        <v>6</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
+      <c r="G55" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I55" s="3"/>
+      <c r="J55" s="14"/>
+    </row>
+    <row r="56" spans="2:10">
+      <c r="B56" s="1">
+        <v>7</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
+      <c r="G56" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I56" s="3"/>
+      <c r="J56" s="14" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="57" spans="2:10">
+      <c r="B57" s="1">
+        <v>8</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3"/>
+      <c r="G57" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H52" s="1" t="s">
+      <c r="H57" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I52" s="13" t="s">
+      <c r="I57" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="J52" s="6"/>
-    </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C54" s="14"/>
-    </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="G55" s="11"/>
-    </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="G56" s="11"/>
+      <c r="J57" s="13" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="59" spans="2:10">
+      <c r="C59" s="12"/>
+    </row>
+    <row r="60" spans="2:10">
+      <c r="G60" s="10"/>
+    </row>
+    <row r="61" spans="2:10">
+      <c r="G61" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B48:C48"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="I45" r:id="rId1" xr:uid="{8F0A5C78-2E3A-4798-93F6-5B692CD25D15}"/>
-    <hyperlink ref="I46" r:id="rId2" xr:uid="{D124E730-358C-4E6F-87F7-20A67083454B}"/>
-    <hyperlink ref="I47" r:id="rId3" xr:uid="{46DA6087-18E8-4243-8F4A-8CF6F55077A3}"/>
-    <hyperlink ref="I48" r:id="rId4" xr:uid="{31B8B28A-8397-4B67-8405-838F48C3074C}"/>
-    <hyperlink ref="I52" r:id="rId5" xr:uid="{FB469A6A-9044-426E-B764-97A4BF043002}"/>
+    <hyperlink ref="I50" r:id="rId1" xr:uid="{8F0A5C78-2E3A-4798-93F6-5B692CD25D15}"/>
+    <hyperlink ref="I51" r:id="rId2" xr:uid="{D124E730-358C-4E6F-87F7-20A67083454B}"/>
+    <hyperlink ref="I52" r:id="rId3" xr:uid="{46DA6087-18E8-4243-8F4A-8CF6F55077A3}"/>
+    <hyperlink ref="I53" r:id="rId4" xr:uid="{31B8B28A-8397-4B67-8405-838F48C3074C}"/>
+    <hyperlink ref="J57" r:id="rId5" display="whm.notificaciones@sanpablo.com.pe" xr:uid="{87B0BDD4-FDE9-494B-9934-4F36FC994471}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>

--- a/docs/shm_diagrama_despliegue.xlsx
+++ b/docs/shm_diagrama_despliegue.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Fuentes SGD\ADG_HHMM v1\ADG_SHM\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C844A09-F634-4AD5-9D42-1DBDAD78C5BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B589F9CD-FC1E-4DCF-9F04-91D167FD613A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{86EF7CFC-75BA-4FD8-A433-F01FE68532FB}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="42">
   <si>
     <t>Componentes</t>
   </si>
@@ -54,9 +54,6 @@
     <t>Acceso</t>
   </si>
   <si>
-    <t>Dominio</t>
-  </si>
-  <si>
     <t>Servidor Aplicaciones 1</t>
   </si>
   <si>
@@ -151,6 +148,12 @@
   </si>
   <si>
     <t>En test  : https://190.12.87.190:8124</t>
+  </si>
+  <si>
+    <t>Dominio (Producción)</t>
+  </si>
+  <si>
+    <t>https://172.30.255.25:8104</t>
   </si>
 </sst>
 </file>
@@ -207,7 +210,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -217,6 +220,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -249,7 +258,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -283,8 +292,24 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -689,8 +714,8 @@
       </c>
     </row>
     <row r="48" spans="2:10" ht="15" customHeight="1">
-      <c r="B48" s="15"/>
-      <c r="C48" s="15"/>
+      <c r="B48" s="20"/>
+      <c r="C48" s="20"/>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
       <c r="F48" s="4"/>
@@ -722,10 +747,10 @@
         <v>7</v>
       </c>
       <c r="I49" s="8" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="J49" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="50" spans="2:10">
@@ -733,21 +758,21 @@
         <v>1</v>
       </c>
       <c r="C50" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D50" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
       <c r="G50" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I50" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J50" s="14"/>
     </row>
@@ -756,21 +781,21 @@
         <v>2</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
       <c r="G51" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H51" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H51" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="I51" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J51" s="14"/>
     </row>
@@ -779,70 +804,70 @@
         <v>3</v>
       </c>
       <c r="C52" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D52" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
       <c r="G52" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H52" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I52" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="J52" s="14"/>
+    </row>
+    <row r="53" spans="2:10">
+      <c r="B53" s="17">
+        <v>4</v>
+      </c>
+      <c r="C53" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="I52" s="13" t="s">
+      <c r="D53" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="E53" s="16"/>
+      <c r="F53" s="16"/>
+      <c r="G53" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="H53" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="I53" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="J52" s="14"/>
-    </row>
-    <row r="53" spans="2:10">
-      <c r="B53" s="1">
-        <v>4</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E53" s="3"/>
-      <c r="F53" s="3"/>
-      <c r="G53" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H53" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I53" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="J53" s="14"/>
+      <c r="J53" s="18"/>
     </row>
     <row r="54" spans="2:10">
       <c r="B54" s="1">
         <v>5</v>
       </c>
       <c r="C54" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D54" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D54" s="2" t="s">
+      <c r="E54" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>22</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I54" s="3"/>
+        <v>11</v>
+      </c>
+      <c r="I54" s="2"/>
       <c r="J54" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="55" spans="2:10">
@@ -850,43 +875,45 @@
         <v>6</v>
       </c>
       <c r="C55" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D55" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
       <c r="G55" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I55" s="3"/>
       <c r="J55" s="14"/>
     </row>
     <row r="56" spans="2:10">
-      <c r="B56" s="1">
+      <c r="B56" s="17">
         <v>7</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="C56" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="D56" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="D56" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E56" s="3"/>
-      <c r="F56" s="3"/>
-      <c r="G56" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H56" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I56" s="3"/>
-      <c r="J56" s="14" t="s">
-        <v>40</v>
+      <c r="E56" s="16"/>
+      <c r="F56" s="16"/>
+      <c r="G56" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="H56" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="I56" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="J56" s="18" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="57" spans="2:10">
@@ -894,24 +921,24 @@
         <v>8</v>
       </c>
       <c r="C57" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D57" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
       <c r="G57" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I57" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="J57" s="13" t="s">
         <v>38</v>
-      </c>
-      <c r="J57" s="13" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="59" spans="2:10">
@@ -933,9 +960,10 @@
     <hyperlink ref="I52" r:id="rId3" xr:uid="{46DA6087-18E8-4243-8F4A-8CF6F55077A3}"/>
     <hyperlink ref="I53" r:id="rId4" xr:uid="{31B8B28A-8397-4B67-8405-838F48C3074C}"/>
     <hyperlink ref="J57" r:id="rId5" display="whm.notificaciones@sanpablo.com.pe" xr:uid="{87B0BDD4-FDE9-494B-9934-4F36FC994471}"/>
+    <hyperlink ref="I56" r:id="rId6" xr:uid="{673D9B88-95B9-442E-A937-AAC9FAF915C9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
-  <drawing r:id="rId7"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId7"/>
+  <drawing r:id="rId8"/>
 </worksheet>
 </file>